--- a/templet/PREMIUM_T_ACCOUNT.xlsx
+++ b/templet/PREMIUM_T_ACCOUNT.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/64cd5bb3604bb353/Desktop/共保志工險/規格書/檔案位子範例/templet/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\Health-and-Injury-Co-Insurance-System\templet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="11_AD4DBB64A54DDB1B405E389605D904C94E90DF19" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E765BAD6-9D1F-40F3-831D-321C50D8D529}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF187148-4CF6-4F05-82E0-91C245782898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="577" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="16380" windowHeight="11295" tabRatio="577" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -82,7 +82,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,6 +144,14 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u val="double"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -153,7 +161,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -249,15 +257,6 @@
       </top>
       <bottom style="medium">
         <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -290,9 +289,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -321,10 +320,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -685,7 +680,7 @@
     </row>
     <row r="5" spans="1:16" ht="21" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="13" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="4"/>
@@ -695,7 +690,7 @@
       <c r="G5" s="4"/>
       <c r="H5" s="5"/>
       <c r="I5" s="4"/>
-      <c r="J5" s="14" t="s">
+      <c r="J5" s="13" t="s">
         <v>5</v>
       </c>
       <c r="K5" s="4"/>
@@ -748,7 +743,7 @@
     </row>
     <row r="13" spans="1:16" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="14" t="s">
         <v>7</v>
       </c>
       <c r="H13" s="8"/>
@@ -789,17 +784,19 @@
       <c r="H20" s="8"/>
       <c r="P20" s="8"/>
     </row>
-    <row r="21" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
       <c r="B21" t="s">
         <v>8</v>
       </c>
+      <c r="G21" s="15"/>
       <c r="H21" s="8"/>
-      <c r="O21" s="13"/>
+      <c r="O21" s="15"/>
       <c r="P21" s="8"/>
     </row>
-    <row r="22" spans="1:16" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="6"/>
+      <c r="G22" s="15"/>
       <c r="H22" s="8"/>
       <c r="P22" s="8"/>
     </row>
